--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C42A6C-D33B-4845-8B67-6EC79D49D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1293975C-67FE-49B3-AF04-1B62EDB85619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Flower Name</t>
   </si>
@@ -78,9 +78,6 @@
     <t>Violeta</t>
   </si>
   <si>
-    <t>Echinopsul</t>
-  </si>
-  <si>
     <t>Sunt foarte multe lucruri intresante despre ea in legatura cu zeii greci, dar mi se pare mai intresant  faptul ca violeta a a fost simbolul folosit de sustinatorii lui dupa ce a fost exilat.  A fost asociat cu ideea revenirii odata cu violetele primaverii.</t>
   </si>
   <si>
@@ -127,6 +124,18 @@
   </si>
   <si>
     <t>https://gardencentrumnet.cdn.shoprenter.hu/custom/gardencentrumnet/image/cache/w900h900wt1q100/plante-perene/echinops_ritro_first6.jpg.webp?lastmod=0.1786104009</t>
+  </si>
+  <si>
+    <t>Echinops</t>
+  </si>
+  <si>
+    <t>https://www.fabricademov.ro/wp-content/uploads/2024/06/Lavandula-angustifolia-1.jpg</t>
+  </si>
+  <si>
+    <t>Lavanda</t>
+  </si>
+  <si>
+    <t>In perioadele de epidemii, oamenii o purtau sau foloseau pentru a combate "aerul rau". In limbajul florilor este un simbol al tandretei, devotamentului, linistii si elegantei.</t>
   </si>
 </sst>
 </file>
@@ -453,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -472,10 +481,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -483,10 +492,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -497,7 +506,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -505,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -522,7 +531,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -533,7 +542,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -544,7 +553,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -558,7 +567,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -566,21 +575,32 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1293975C-67FE-49B3-AF04-1B62EDB85619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F8E5C4-522C-44CD-A05D-C6097E11EDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Flower Name</t>
   </si>
@@ -96,9 +96,6 @@
     <t>https://www.enrose.ro/wp-content/uploads/2024/01/orhidee-roz1.jpeg</t>
   </si>
   <si>
-    <t>https://bulbi-flori.ro/wp-content/uploads/2021/10/Trandafir-pomisor-Fragrant-rosu.jpg</t>
-  </si>
-  <si>
     <t>Van Gogh Image Link</t>
   </si>
   <si>
@@ -136,6 +133,15 @@
   </si>
   <si>
     <t>In perioadele de epidemii, oamenii o purtau sau foloseau pentru a combate "aerul rau". In limbajul florilor este un simbol al tandretei, devotamentului, linistii si elegantei.</t>
+  </si>
+  <si>
+    <t>https://i.pinimg.com/736x/bb/88/ae/bb88ae501ded96d641a2b2e70bc7d41d.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.micr.io/qUKva/full/1280,/0/default.jpg</t>
+  </si>
+  <si>
+    <t>https://iiif.micr.io/TGOHC/full/1800,/0/default.webp</t>
   </si>
 </sst>
 </file>
@@ -484,7 +490,7 @@
         <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -506,7 +512,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -517,10 +526,10 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -531,7 +540,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -542,7 +551,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -553,7 +562,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -567,7 +576,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -578,29 +587,32 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F8E5C4-522C-44CD-A05D-C6097E11EDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF240011-9EC8-4280-A676-CDD10AE14BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Flower Name</t>
   </si>
@@ -142,6 +142,24 @@
   </si>
   <si>
     <t>https://iiif.micr.io/TGOHC/full/1800,/0/default.webp</t>
+  </si>
+  <si>
+    <t>Iberis(Lilicel)</t>
+  </si>
+  <si>
+    <t>In limbajul florilor reprezintă indiferenta. In contrast cu asta, ea este o planta care poate crește in sol pietros si uscat. Astfel indiferență poate fi interpretat ca: "Pot sa înfloresc chiar daca lumea din jurul meu nu este blândă</t>
+  </si>
+  <si>
+    <t>https://apps.rhs.org.uk/plantselectorimages/detail/visi22809.jpg</t>
+  </si>
+  <si>
+    <t>Nufar</t>
+  </si>
+  <si>
+    <t>In Feng Shui apa reprezinta curgerea vietii. Nufarul nu incearca sa opreasca apa, ci invata sa pluteasca pe ea. Este un simbol al linistii care nu vine din lipsa problemelor, ci a capacitati de a nu te scufunda in ele.</t>
+  </si>
+  <si>
+    <t>https://www.royalplant.ro/211/nufar-nymphaea-marliacea-albida.jpg</t>
   </si>
 </sst>
 </file>
@@ -468,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -615,6 +633,28 @@
         <v>38</v>
       </c>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF240011-9EC8-4280-A676-CDD10AE14BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882D47E6-2A4E-4F88-83EF-CAC3DC1303A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Flower Name</t>
   </si>
@@ -160,6 +160,24 @@
   </si>
   <si>
     <t>https://www.royalplant.ro/211/nufar-nymphaea-marliacea-albida.jpg</t>
+  </si>
+  <si>
+    <t>Azalee</t>
+  </si>
+  <si>
+    <t>https://tuia.ro/wp-content/uploads-webpc/uploads/2024/02/20200602_132243-2-3.png.webp</t>
+  </si>
+  <si>
+    <t>Floare de astazi este Azaleea. In limbajul florilor este asociata cu grija fata de cineva, delicatea si afectiune. De aici i sa asociat si un mesaj: "Ai grija de tine pentru mine". Exista si un contrast deoarece ele sunt toxice daca le ingerezi, sunt asociate si cu prudenta. Astfel transmite si ideea unei limite care nu trebuie incalcata.</t>
+  </si>
+  <si>
+    <t>https://pepinieraromaniei.ro/cdn/shop/files/Bulbi-de-Caldaruse-Aquilegia-Spring-Magic-Navy-and-4.jpg?v=1782371142</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Aquilegia (Caldarusa). In limba latina este asociata cu "Aquila"(Vultur), fiindca petalelor florii ar semana cu gherele unui vultur. In engleza insa este  "columbine" , de la porumbel. Deci aceeasi floare e vazuta si ca vultur si ca porumbel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aquilegia </t>
   </si>
 </sst>
 </file>
@@ -486,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -655,6 +673,28 @@
         <v>44</v>
       </c>
     </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882D47E6-2A4E-4F88-83EF-CAC3DC1303A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CFBAF2-C04B-4ABF-B6B0-A118EA3FE26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Flower Name</t>
   </si>
@@ -168,16 +168,28 @@
     <t>https://tuia.ro/wp-content/uploads-webpc/uploads/2024/02/20200602_132243-2-3.png.webp</t>
   </si>
   <si>
-    <t>Floare de astazi este Azaleea. In limbajul florilor este asociata cu grija fata de cineva, delicatea si afectiune. De aici i sa asociat si un mesaj: "Ai grija de tine pentru mine". Exista si un contrast deoarece ele sunt toxice daca le ingerezi, sunt asociate si cu prudenta. Astfel transmite si ideea unei limite care nu trebuie incalcata.</t>
-  </si>
-  <si>
     <t>https://pepinieraromaniei.ro/cdn/shop/files/Bulbi-de-Caldaruse-Aquilegia-Spring-Magic-Navy-and-4.jpg?v=1782371142</t>
   </si>
   <si>
-    <t>Floarea de astazi este Aquilegia (Caldarusa). In limba latina este asociata cu "Aquila"(Vultur), fiindca petalelor florii ar semana cu gherele unui vultur. In engleza insa este  "columbine" , de la porumbel. Deci aceeasi floare e vazuta si ca vultur si ca porumbel.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Aquilegia </t>
+  </si>
+  <si>
+    <t>In limba latina este asociata cu "Aquila"(Vultur), fiindca petalelor florii ar semana cu gherele unui vultur. In engleza insa este  "columbine" , de la porumbel. Deci aceeasi floare e vazuta si ca vultur si ca porumbel.</t>
+  </si>
+  <si>
+    <t>In limbajul florilor este asociata cu grija fata de cineva, delicatea si afectiune. De aici i sa asociat si un mesaj: "Ai grija de tine pentru mine". Exista si un contrast deoarece ele sunt toxice daca le ingerezi, sunt asociate si cu prudenta. Astfel transmite si ideea unei limite care nu trebuie incalcata.</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcQoqPnA1oLu6JgxSxatDjJwjGZ5fN8vnfFkpjTQejkwS4A5BNIf4iCLF64&amp;s=10</t>
+  </si>
+  <si>
+    <t>Panseluta</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Panseluta. Cuvantul englezesc "pansy" provine din francesul "pensee" care inseamna "gand". In limbajul florilor, panseluta transmite mesajul de "ma gandesc la tine".</t>
+  </si>
+  <si>
+    <t>Bonus: Ea este asociata si cu magia iubirii in unele traditii europene. Asta apare si in "Visul unei notpii de vara" de Shakespear, unde sucul unei flori este folosit pentru a face pe cineva sa se indragosteasca</t>
   </si>
 </sst>
 </file>
@@ -504,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -678,7 +690,7 @@
         <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
@@ -686,13 +698,27 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
         <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CFBAF2-C04B-4ABF-B6B0-A118EA3FE26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E921D8-8526-48FA-8335-325398C0D94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
   <si>
     <t>Flower Name</t>
   </si>
@@ -190,6 +190,51 @@
   </si>
   <si>
     <t>Bonus: Ea este asociata si cu magia iubirii in unele traditii europene. Asta apare si in "Visul unei notpii de vara" de Shakespear, unde sucul unei flori este folosit pentru a face pe cineva sa se indragosteasca</t>
+  </si>
+  <si>
+    <t>Regina-Noptii</t>
+  </si>
+  <si>
+    <t>https://www.whiteflowerfarm.com/mas_assets/cache/image/3/7/f/c/14332.Jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ea apartine aceluiasi gen ca si tutunul - Nicotiana. Din cauza asta in engleza ii se spune "jasmine tabacco" sau "flowering tobacco". </t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>Eustoma</t>
+  </si>
+  <si>
+    <t>https://mullerseeds.ro/app/uploads/2024/12/FRS785-01.jpg</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Eustoma. Seamana cu trandafirul, dar nu este ruda cu el. Numele provide din greaca: "eu" inseamna "bun/frumos", iar "stoma" inseamna "gura". Astfel numele poate fi interpretat ca "gura frumoasa". Pe langa asta, simbolistica are legatura cu contrastul ei, ea pare delicata, dar este o floare de camp. Asta simbolizeaza ca isi pastreaza delicatetea chiar daca a fost obligata sa fie puternica.</t>
+  </si>
+  <si>
+    <t>https://docaperene.ro/cdn/shop/files/ochiul-fetei-coreopsis-grandiflora-sunfire-yellow-red-653181.jpg?v=1748507929</t>
+  </si>
+  <si>
+    <t>Ochiul-Fetei (Coreopsis)</t>
+  </si>
+  <si>
+    <t>Floarea de ieri era Ochiul-Fetei (Coreopsis). Numele Coreopsis vine din grecescul "koris", care inseamna "plosnita" si "opsis" care inseamna "aspect", din cauza ca semintele seamana cu micii insecte. Ea a fost folosita si ca planta tinctoriala, pentru pigmentii galbeni, portocalii si rosiatici.</t>
+  </si>
+  <si>
+    <t>Trillium</t>
+  </si>
+  <si>
+    <t>https://cdn.pixabay.com/photo/2017/06/22/10/19/the-nano-the-trillium-2430309_1280.jpg</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Trillium. Ce e intresant la ea este faptul ca totul se invarte in jurul cifre trei. Numele vine din latina si face referire la trei, are 3 petale, 3 sepale, iar frunzele sunt in grupuri de 3</t>
   </si>
 </sst>
 </file>
@@ -516,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.7265625" customWidth="1"/>
@@ -721,6 +766,70 @@
         <v>51</v>
       </c>
     </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E921D8-8526-48FA-8335-325398C0D94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F069492-46D3-49CF-BE4A-B2A2013172CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$24</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Flower Name</t>
   </si>
@@ -186,9 +189,6 @@
     <t>Panseluta</t>
   </si>
   <si>
-    <t>Floarea de astazi este Panseluta. Cuvantul englezesc "pansy" provine din francesul "pensee" care inseamna "gand". In limbajul florilor, panseluta transmite mesajul de "ma gandesc la tine".</t>
-  </si>
-  <si>
     <t>Bonus: Ea este asociata si cu magia iubirii in unele traditii europene. Asta apare si in "Visul unei notpii de vara" de Shakespear, unde sucul unei flori este folosit pentru a face pe cineva sa se indragosteasca</t>
   </si>
   <si>
@@ -216,25 +216,37 @@
     <t>https://mullerseeds.ro/app/uploads/2024/12/FRS785-01.jpg</t>
   </si>
   <si>
-    <t>Floarea de astazi este Eustoma. Seamana cu trandafirul, dar nu este ruda cu el. Numele provide din greaca: "eu" inseamna "bun/frumos", iar "stoma" inseamna "gura". Astfel numele poate fi interpretat ca "gura frumoasa". Pe langa asta, simbolistica are legatura cu contrastul ei, ea pare delicata, dar este o floare de camp. Asta simbolizeaza ca isi pastreaza delicatetea chiar daca a fost obligata sa fie puternica.</t>
-  </si>
-  <si>
     <t>https://docaperene.ro/cdn/shop/files/ochiul-fetei-coreopsis-grandiflora-sunfire-yellow-red-653181.jpg?v=1748507929</t>
   </si>
   <si>
     <t>Ochiul-Fetei (Coreopsis)</t>
   </si>
   <si>
-    <t>Floarea de ieri era Ochiul-Fetei (Coreopsis). Numele Coreopsis vine din grecescul "koris", care inseamna "plosnita" si "opsis" care inseamna "aspect", din cauza ca semintele seamana cu micii insecte. Ea a fost folosita si ca planta tinctoriala, pentru pigmentii galbeni, portocalii si rosiatici.</t>
-  </si>
-  <si>
     <t>Trillium</t>
   </si>
   <si>
     <t>https://cdn.pixabay.com/photo/2017/06/22/10/19/the-nano-the-trillium-2430309_1280.jpg</t>
   </si>
   <si>
-    <t>Floarea de astazi este Trillium. Ce e intresant la ea este faptul ca totul se invarte in jurul cifre trei. Numele vine din latina si face referire la trei, are 3 petale, 3 sepale, iar frunzele sunt in grupuri de 3</t>
+    <t>Eschscholzia</t>
+  </si>
+  <si>
+    <t>Ce e intresant la ea este faptul ca totul se invarte in jurul cifre trei. Numele vine din latina si face referire la trei, are 3 petale, 3 sepale, iar frunzele sunt in grupuri de 3</t>
+  </si>
+  <si>
+    <t>Numele Coreopsis vine din grecescul "koris", care inseamna "plosnita" si "opsis" care inseamna "aspect", din cauza ca semintele seamana cu micii insecte. Ea a fost folosita si ca planta tinctoriala, pentru pigmentii galbeni, portocalii si rosiatici.</t>
+  </si>
+  <si>
+    <t>Seamana cu trandafirul, dar nu este ruda cu el. Numele provide din greaca: "eu" inseamna "bun/frumos", iar "stoma" inseamna "gura". Astfel numele poate fi interpretat ca "gura frumoasa". Pe langa asta, simbolistica are legatura cu contrastul ei, ea pare delicata, dar este o floare de camp. Asta simbolizeaza ca isi pastreaza delicatetea chiar daca a fost obligata sa fie puternica.</t>
+  </si>
+  <si>
+    <t>Cuvantul englezesc "pansy" provine din francesul "pensee" care inseamna "gand". In limbajul florilor, panseluta transmite mesajul de "ma gandesc la tine".</t>
+  </si>
+  <si>
+    <t>https://www.gardenia.net/wp-content/uploads/2023/05/eschscholzia-californica-california-poppy-780x520.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce e intresant e faptul ca isi inchide petalele cand vremea e rea sau noapte si le deschide cand e lumina puternica. Este floarea oficiala a  Californiei, si pe 6 aprilie este sarbatorita drept "California Poppy Day". Ca si simbolistica, este asociata cu pacea, visarea si speranta. </t>
   </si>
 </sst>
 </file>
@@ -757,10 +769,10 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>51</v>
@@ -768,69 +780,76 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
         <v>55</v>
-      </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
         <v>61</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" t="s">
         <v>67</v>
       </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>66</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E24" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F069492-46D3-49CF-BE4A-B2A2013172CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56C6C19-916C-4B9B-B1A4-8032A3EAE723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,19 +16,30 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$24</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>Flower Name</t>
   </si>
@@ -204,9 +215,6 @@
     <t>e</t>
   </si>
   <si>
-    <t>s</t>
-  </si>
-  <si>
     <t>i</t>
   </si>
   <si>
@@ -247,6 +255,87 @@
   </si>
   <si>
     <t xml:space="preserve">Ce e intresant e faptul ca isi inchide petalele cand vremea e rea sau noapte si le deschide cand e lumina puternica. Este floarea oficiala a  Californiei, si pe 6 aprilie este sarbatorita drept "California Poppy Day". Ca si simbolistica, este asociata cu pacea, visarea si speranta. </t>
+  </si>
+  <si>
+    <t>Salvia</t>
+  </si>
+  <si>
+    <t>https://gardencentrumnet.cdn.shoprenter.hu/custom/gardencentrumnet/image/cache/w900h900wt1q100/plante-perene/salvia.png.webp?lastmod=0.1786104009</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Salvia. Numele ei provine din latinescul salvare/salvus, cu sensul de "a salva", "a vindeca", "a fi sanatos". In limbajul florilor simbolizeaza intelepciune si longevitate, asta si datorita numelui in engleza "Sage". Iar in Evul Mediu, circula expresia "Cur moriatur homo cui Salvia crescit in horto?" ce se traduce in "Cum sa moara un om caruia ii creste salvie in grădina?"</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>5.08.2026</t>
+  </si>
+  <si>
+    <t>6.08.2026</t>
+  </si>
+  <si>
+    <t>7.08.2026</t>
+  </si>
+  <si>
+    <t>8.08.2026</t>
+  </si>
+  <si>
+    <t>9.08.2026</t>
+  </si>
+  <si>
+    <t>10.08.2026</t>
+  </si>
+  <si>
+    <t>11.08.2026</t>
+  </si>
+  <si>
+    <t>12.08.2026</t>
+  </si>
+  <si>
+    <t>13.08.2026</t>
+  </si>
+  <si>
+    <t>14.08.2026</t>
+  </si>
+  <si>
+    <t>15.08.2026</t>
+  </si>
+  <si>
+    <t>16.08.2026</t>
+  </si>
+  <si>
+    <t>17.08.2026</t>
+  </si>
+  <si>
+    <t>18.08.2026</t>
+  </si>
+  <si>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>20.08.2026</t>
+  </si>
+  <si>
+    <t>21.08.2026</t>
+  </si>
+  <si>
+    <t>22.08.2026</t>
+  </si>
+  <si>
+    <t>23.08.2026</t>
+  </si>
+  <si>
+    <t>24.08.2026</t>
+  </si>
+  <si>
+    <t>25.08.2026</t>
+  </si>
+  <si>
+    <t>26.08.2026</t>
+  </si>
+  <si>
+    <t>27.08.2026</t>
   </si>
 </sst>
 </file>
@@ -290,9 +379,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,283 +664,372 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" customWidth="1"/>
-    <col min="2" max="2" width="67.36328125" customWidth="1"/>
-    <col min="3" max="3" width="25.6328125" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" customWidth="1"/>
+    <col min="3" max="3" width="67.36328125" customWidth="1"/>
+    <col min="4" max="4" width="25.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>18</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>43</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>49</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
         <v>52</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
         <v>70</v>
       </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" t="s">
         <v>72</v>
       </c>
-      <c r="D21" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F24" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56C6C19-916C-4B9B-B1A4-8032A3EAE723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F02B8FC-6CB5-4A33-8FDB-3CDFC6561533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>Flower Name</t>
   </si>
@@ -212,9 +212,6 @@
     <t xml:space="preserve">Ea apartine aceluiasi gen ca si tutunul - Nicotiana. Din cauza asta in engleza ii se spune "jasmine tabacco" sau "flowering tobacco". </t>
   </si>
   <si>
-    <t>e</t>
-  </si>
-  <si>
     <t>i</t>
   </si>
   <si>
@@ -263,9 +260,6 @@
     <t>https://gardencentrumnet.cdn.shoprenter.hu/custom/gardencentrumnet/image/cache/w900h900wt1q100/plante-perene/salvia.png.webp?lastmod=0.1786104009</t>
   </si>
   <si>
-    <t>Floarea de astazi este Salvia. Numele ei provine din latinescul salvare/salvus, cu sensul de "a salva", "a vindeca", "a fi sanatos". In limbajul florilor simbolizeaza intelepciune si longevitate, asta si datorita numelui in engleza "Sage". Iar in Evul Mediu, circula expresia "Cur moriatur homo cui Salvia crescit in horto?" ce se traduce in "Cum sa moara un om caruia ii creste salvie in grădina?"</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -336,6 +330,18 @@
   </si>
   <si>
     <t>27.08.2026</t>
+  </si>
+  <si>
+    <t>Echinacea</t>
+  </si>
+  <si>
+    <t>Numele ei provine din latinescul salvare/salvus, cu sensul de "a salva", "a vindeca", "a fi sanatos". In limbajul florilor simbolizeaza intelepciune si longevitate, asta si datorita numelui in engleza "Sage". Iar in Evul Mediu, circula expresia "Cur moriatur homo cui Salvia crescit in horto?" ce se traduce in "Cum sa moara un om caruia ii creste salvie in grădina?"</t>
+  </si>
+  <si>
+    <t>Floarea de astazi este Echinacea. "Echinacea" provine din grecescul "eckhinos" care inseamna arici. Ea a fost folosita de popoare indigene din America pentru rani, muscaturi si dureri. Conform studiilor, are un mic impact impotriva racile si sustine imunitate. Iar, floarea in sine este alta luptatoare.</t>
+  </si>
+  <si>
+    <t>https://ac45e9e4.delivery.rocketcdn.me/wp-content/uploads/2026/01/Echinacea-Rudbeckia-purpurea-Grandiflora-Magnus.png.webp</t>
   </si>
 </sst>
 </file>
@@ -379,11 +385,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,7 +680,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -694,8 +699,8 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>76</v>
+      <c r="A2" t="s">
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -708,8 +713,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>77</v>
+      <c r="A3" t="s">
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -725,8 +730,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>78</v>
+      <c r="A4" t="s">
+        <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -742,8 +747,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>79</v>
+      <c r="A5" t="s">
+        <v>77</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -756,8 +761,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>80</v>
+      <c r="A6" t="s">
+        <v>78</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -770,8 +775,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>81</v>
+      <c r="A7" t="s">
+        <v>79</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -784,8 +789,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>82</v>
+      <c r="A8" t="s">
+        <v>80</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -801,8 +806,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
+      <c r="A9" t="s">
+        <v>81</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -815,8 +820,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
+      <c r="A10" t="s">
+        <v>82</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -829,8 +834,8 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>85</v>
+      <c r="A11" t="s">
+        <v>83</v>
       </c>
       <c r="B11" t="s">
         <v>34</v>
@@ -846,8 +851,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>86</v>
+      <c r="A12" t="s">
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
@@ -860,8 +865,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>87</v>
+      <c r="A13" t="s">
+        <v>85</v>
       </c>
       <c r="B13" t="s">
         <v>42</v>
@@ -874,8 +879,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>88</v>
+      <c r="A14" t="s">
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>45</v>
@@ -888,8 +893,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>89</v>
+      <c r="A15" t="s">
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
@@ -902,14 +907,14 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>90</v>
+      <c r="A16" t="s">
+        <v>88</v>
       </c>
       <c r="B16" t="s">
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
         <v>53</v>
@@ -919,8 +924,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>91</v>
+      <c r="A17" t="s">
+        <v>89</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
@@ -933,89 +938,95 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+      <c r="A18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>92</v>
       </c>
-      <c r="B18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>93</v>
       </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>94</v>
       </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>95</v>
       </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>96</v>
       </c>
-      <c r="B22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">

--- a/excel_to_json/flowers.xlsx
+++ b/excel_to_json/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitit\Desktop\flowers-site\excel_to_json\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F02B8FC-6CB5-4A33-8FDB-3CDFC6561533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A244337E-AEA1-44D4-89EE-00D41B9A43EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>Flower Name</t>
   </si>
@@ -338,10 +338,58 @@
     <t>Numele ei provine din latinescul salvare/salvus, cu sensul de "a salva", "a vindeca", "a fi sanatos". In limbajul florilor simbolizeaza intelepciune si longevitate, asta si datorita numelui in engleza "Sage". Iar in Evul Mediu, circula expresia "Cur moriatur homo cui Salvia crescit in horto?" ce se traduce in "Cum sa moara un om caruia ii creste salvie in grădina?"</t>
   </si>
   <si>
-    <t>Floarea de astazi este Echinacea. "Echinacea" provine din grecescul "eckhinos" care inseamna arici. Ea a fost folosita de popoare indigene din America pentru rani, muscaturi si dureri. Conform studiilor, are un mic impact impotriva racile si sustine imunitate. Iar, floarea in sine este alta luptatoare.</t>
-  </si>
-  <si>
     <t>https://ac45e9e4.delivery.rocketcdn.me/wp-content/uploads/2026/01/Echinacea-Rudbeckia-purpurea-Grandiflora-Magnus.png.webp</t>
+  </si>
+  <si>
+    <t>Cea mai rară piatra prețioasă/minerala din lume este Painite. A fost descoperită in 1950 in Myanmar</t>
+  </si>
+  <si>
+    <t>Letter</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Ixia</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcRUDkuqqLjpcTU_iPR9tL_T0GV-KYVRz2HO3AmmlfSfCQ&amp;s=10</t>
+  </si>
+  <si>
+    <t>"Echinacea" provine din grecescul "eckhinos" care inseamna arici. Ea a fost folosita de popoare indigene din America pentru rani, muscaturi si dureri. Conform studiilor, are un mic impact impotriva racile si sustine imunitate. Iar, floarea in sine este alta luptatoare.</t>
+  </si>
+  <si>
+    <t>Este originara exclusiv din Africa de Sud. Exista un tip de Ixia de o culoare rara in natura - turcoaz-verzui ( ca in poza). Iar un lucru intresant este ca fiind din Africa, ea e influenta de incendiile periodice. Radacina ramane intreaga, iar dupa trecerea periodei nefavorabile "renaste" la viata.</t>
   </si>
 </sst>
 </file>
@@ -669,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.54296875" customWidth="1"/>
@@ -678,7 +726,7 @@
     <col min="4" max="4" width="25.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -697,8 +745,11 @@
       <c r="F1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -711,8 +762,11 @@
       <c r="E2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -728,8 +782,11 @@
       <c r="F3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>76</v>
       </c>
@@ -745,8 +802,11 @@
       <c r="F4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -759,8 +819,11 @@
       <c r="E5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -773,8 +836,11 @@
       <c r="E6" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -787,8 +853,11 @@
       <c r="E7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>80</v>
       </c>
@@ -804,8 +873,11 @@
       <c r="E8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -818,8 +890,11 @@
       <c r="E9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>82</v>
       </c>
@@ -832,8 +907,11 @@
       <c r="E10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H10" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>83</v>
       </c>
@@ -849,8 +927,11 @@
       <c r="F11" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>84</v>
       </c>
@@ -863,8 +944,11 @@
       <c r="E12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -877,8 +961,11 @@
       <c r="E13" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>86</v>
       </c>
@@ -891,8 +978,11 @@
       <c r="E14" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -905,8 +995,11 @@
       <c r="E15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>88</v>
       </c>
@@ -922,8 +1015,11 @@
       <c r="E16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>89</v>
       </c>
@@ -936,8 +1032,11 @@
       <c r="E17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -950,8 +1049,11 @@
       <c r="E18" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -964,8 +1066,11 @@
       <c r="E19" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -978,8 +1083,11 @@
       <c r="E20" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -992,8 +1100,11 @@
       <c r="E21" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -1006,8 +1117,11 @@
       <c r="E22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -1015,27 +1129,42 @@
         <v>97</v>
       </c>
       <c r="C23" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s">
         <v>99</v>
       </c>
-      <c r="E23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="H23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>96</v>
       </c>
       <c r="B24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>114</v>
+      </c>
+      <c r="H24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
     </row>
   </sheetData>
